--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104682_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104682_W25.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1244</v>
+        <v>3.9906</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8284</v>
+        <v>2.4175</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2961</v>
+        <v>1.5731</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8008</v>
+        <v>5.786</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8701</v>
+        <v>2.8981</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0693</v>
+        <v>2.8878</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4101</v>
+        <v>6.817</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5572</v>
+        <v>3.0714</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8529</v>
+        <v>3.7456</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6094000000000001</v>
+        <v>-1.031</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3129</v>
+        <v>-0.1733</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9222</v>
+        <v>-0.8578</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-5.6908</v>
       </c>
       <c r="R2" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7773</v>
+        <v>0.0743</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5939</v>
+        <v>0.2018</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1834</v>
+        <v>-0.1275</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2726</v>
+        <v>3.443</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6296</v>
+        <v>2.7174</v>
       </c>
       <c r="F3" t="n">
-        <v>0.643</v>
+        <v>0.7256</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3151</v>
+        <v>2.3084</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1068</v>
+        <v>3.0994</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7917</v>
+        <v>-0.791</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8582</v>
+        <v>2.8384</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5326</v>
+        <v>3.5163</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5431</v>
+        <v>-0.53</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4301</v>
+        <v>-0.2508</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3478</v>
+        <v>-0.2301</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0823</v>
+        <v>-0.0207</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9367</v>
+        <v>2.9773</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5824</v>
+        <v>0.6826</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3543</v>
+        <v>2.2947</v>
       </c>
       <c r="G4" t="n">
-        <v>5.8018</v>
+        <v>0.7971</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9018</v>
+        <v>0.8702</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9</v>
+        <v>-0.0732</v>
       </c>
       <c r="J4" t="n">
-        <v>6.8562</v>
+        <v>1.382</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0926</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>3.7636</v>
+        <v>0.8411</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0543</v>
+        <v>-0.5849</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1908</v>
+        <v>0.3294</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8636</v>
+        <v>-0.9143</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.9488</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.6708</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.009</v>
+        <v>0.6355</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6956</v>
+        <v>0.4874</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3133</v>
+        <v>0.1481</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6657</v>
+        <v>2.649</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2334</v>
+        <v>1.9661</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5677</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2744</v>
+        <v>-0.4471</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5511</v>
+        <v>-0.0144</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2768</v>
+        <v>-0.4326</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9687</v>
+        <v>1.7736</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0087</v>
+        <v>0.7617</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.04</v>
+        <v>1.012</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6944</v>
+        <v>-2.2207</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4576</v>
+        <v>-0.7761</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2368</v>
+        <v>-1.4446</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>2.9592</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5086</v>
+        <v>0.0278</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1039</v>
+        <v>0.0834</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4047</v>
+        <v>-0.0556</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9320000000000001</v>
+        <v>1.2472</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>1.2472</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.934</v>
+        <v>2.3834</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4033</v>
+        <v>1.523</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7524</v>
+        <v>0.7487</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0158</v>
+        <v>2.0135</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2635</v>
+        <v>-1.2647</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5409</v>
+        <v>0.5179</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0016</v>
+        <v>1.9855</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2115</v>
+        <v>0.2308</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4043</v>
+        <v>-0.9604</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5565</v>
+        <v>-0.2023</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8478</v>
+        <v>-0.7581</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6331</v>
+        <v>2.2642</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2298</v>
+        <v>3.055</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4033</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4345</v>
+        <v>0.2786</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0159</v>
+        <v>1.5537</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4186</v>
+        <v>-1.275</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8062</v>
+        <v>1.9546</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7721</v>
+        <v>1.9995</v>
       </c>
       <c r="L7" t="n">
-        <v>1.034</v>
+        <v>-0.0449</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2407</v>
+        <v>-1.6759</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.788</v>
+        <v>-0.4458</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4526</v>
+        <v>-1.2301</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9488</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0005</v>
+        <v>1.0962</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6956</v>
+        <v>0.9427</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3049</v>
+        <v>0.1535</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2534</v>
+        <v>-0.9317</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2534</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4267</v>
+        <v>2.0629</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8704</v>
+        <v>0.75</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4437</v>
+        <v>1.3129</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1335</v>
+        <v>1.171</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5831</v>
+        <v>0.9848</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7166</v>
+        <v>0.1862</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2219</v>
+        <v>1.4994</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4258</v>
+        <v>0.9858</v>
       </c>
       <c r="L8" t="n">
-        <v>2.796</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0884</v>
+        <v>-0.3284</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0089</v>
+        <v>-0.0009</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0795</v>
+        <v>-0.3275</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3593</v>
+        <v>-0.3357</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7561</v>
+        <v>-0.156</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3968</v>
+        <v>-0.1797</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1607</v>
+        <v>0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0.5447</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2423</v>
+        <v>1.2073</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1126</v>
+        <v>1.5592</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1297</v>
+        <v>-0.3519</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1663</v>
+        <v>1.138</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9797</v>
+        <v>-0.5749</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1866</v>
+        <v>1.7129</v>
       </c>
       <c r="J9" t="n">
-        <v>1.517</v>
+        <v>3.202</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9973</v>
+        <v>0.4169</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5197000000000001</v>
+        <v>2.7851</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3507</v>
+        <v>-2.064</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0176</v>
+        <v>-0.9918</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3331</v>
+        <v>-1.0722</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1508</v>
+        <v>0.1392</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8166</v>
+        <v>0.4757</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3342</v>
+        <v>-0.3366</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.3937</v>
       </c>
       <c r="E10" t="n">
-        <v>1.626</v>
+        <v>1.2686</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5423</v>
+        <v>-0.8748</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0103</v>
+        <v>0.8213</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0288</v>
+        <v>1.6687</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0391</v>
+        <v>-0.8475</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6331</v>
+        <v>2.025</v>
       </c>
       <c r="K10" t="n">
-        <v>1.5341</v>
+        <v>1.9133</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.901</v>
+        <v>0.1117</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6434</v>
+        <v>-1.2037</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5053</v>
+        <v>-0.2446</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1381</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9475</v>
+        <v>-0.4762</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0998</v>
+        <v>-0.3695</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8478</v>
+        <v>-0.1067</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>-0.387</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0732</v>
+        <v>0.2556</v>
       </c>
       <c r="E11" t="n">
-        <v>1.092</v>
+        <v>1.6723</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0188</v>
+        <v>-1.4167</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8192</v>
+        <v>-1.0068</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6695</v>
+        <v>1.031</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-2.0377</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0341</v>
+        <v>0.6111</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9222</v>
+        <v>1.5201</v>
       </c>
       <c r="L11" t="n">
-        <v>0.112</v>
+        <v>-0.909</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2149</v>
+        <v>-1.6179</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2526</v>
+        <v>-0.4891</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-1.1287</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7876</v>
+        <v>-0.7864</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5565</v>
+        <v>-0.0283</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2311</v>
+        <v>-0.7581</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3856</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.7071</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9384</v>
+        <v>-1.6427</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0313</v>
+        <v>-1.5184</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9071</v>
+        <v>-0.1243</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.1206</v>
+        <v>-2.163</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.388</v>
+        <v>-2.163</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7326</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.6898</v>
+        <v>-1.3624</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.9781</v>
+        <v>-2.4346</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7117</v>
+        <v>1.0722</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4308</v>
+        <v>-0.8006</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4099</v>
+        <v>0.2716</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0209</v>
+        <v>-1.0722</v>
       </c>
       <c r="P12" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9139</v>
+        <v>-1.0731</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6585</v>
+        <v>-0.156</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7446</v>
+        <v>-0.9171</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.4973</v>
+        <v>-3.3313</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1552</v>
+        <v>-1.5043</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3421</v>
+        <v>-1.827</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.1689</v>
+        <v>-4.1231</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1689</v>
+        <v>-2.3922</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-1.7309</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.3386</v>
+        <v>-2.7049</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.4181</v>
+        <v>-1.9897</v>
       </c>
       <c r="L13" t="n">
-        <v>1.0795</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8302</v>
+        <v>-1.4182</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2493</v>
+        <v>-0.4025</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0795</v>
+        <v>-1.0157</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9163</v>
+        <v>0.5155</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8166</v>
+        <v>1.2005</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0997</v>
+        <v>-0.6851</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.9566</v>
+        <v>16.653</v>
       </c>
       <c r="E14" t="n">
-        <v>13.5488</v>
+        <v>13.9264</v>
       </c>
       <c r="F14" t="n">
-        <v>2.408</v>
+        <v>2.726800000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>5.329199999999999</v>
+        <v>5.3091</v>
       </c>
       <c r="H14" t="n">
-        <v>8.967700000000001</v>
+        <v>8.974900000000002</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.6387</v>
+        <v>-3.6657</v>
       </c>
       <c r="J14" t="n">
-        <v>18.818</v>
+        <v>18.5537</v>
       </c>
       <c r="K14" t="n">
-        <v>12.448</v>
+        <v>12.287</v>
       </c>
       <c r="L14" t="n">
-        <v>6.3698</v>
+        <v>6.266699999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-13.4888</v>
+        <v>-13.2445</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.4801</v>
+        <v>-3.312</v>
       </c>
       <c r="O14" t="n">
-        <v>-10.0084</v>
+        <v>-9.932500000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>10.2077</v>
+        <v>10.2437</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.61</v>
+        <v>-13.658</v>
       </c>
       <c r="R14" t="n">
-        <v>23.8176</v>
+        <v>23.9016</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.087</v>
+        <v>-1.3941</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5274</v>
+        <v>2.2493</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.6144</v>
+        <v>-3.6436</v>
       </c>
       <c r="V14" t="n">
-        <v>2.5067</v>
+        <v>2.4944</v>
       </c>
       <c r="W14" t="n">
-        <v>6.8133</v>
+        <v>6.7809</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.3066</v>
+        <v>-4.2865</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.6603</v>
+        <v>5.7375</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9196</v>
+        <v>5.7721</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2594</v>
+        <v>-0.0346</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2369</v>
+        <v>2.2313</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6985</v>
+        <v>1.692</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5384</v>
+        <v>0.5393</v>
       </c>
       <c r="J15" t="n">
-        <v>3.723</v>
+        <v>3.6912</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0465</v>
+        <v>2.0232</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4861</v>
+        <v>-1.4599</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6087</v>
+        <v>1.6852</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1039</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5048</v>
+        <v>0.6937</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,22 +1657,22 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3021</v>
+        <v>0.1802</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3717</v>
+        <v>0.2499</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1684,31 +1684,31 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1071</v>
+        <v>-0.0185</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1766</v>
+        <v>0.0512</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2193</v>
+        <v>-0.1149</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4275</v>
+        <v>0.4237</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2082</v>
+        <v>-0.5386</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.77</v>
+        <v>-0.7618</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3089</v>
+        <v>-0.3047</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4611</v>
+        <v>-0.4571</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.011</v>
+        <v>-0.0174</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1976</v>
+        <v>-0.2036</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.759</v>
+        <v>-0.7444</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5356</v>
+        <v>0.1917</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4386</v>
+        <v>0.4411</v>
       </c>
       <c r="U17" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.2494</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>K. COOK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0125</v>
+        <v>-0.3404</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1663</v>
+        <v>-0.1323</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1537</v>
+        <v>-0.2081</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0504</v>
+        <v>0.3018</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5195</v>
+        <v>0.9797</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4691</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6089</v>
+        <v>0.5868</v>
       </c>
       <c r="K18" t="n">
-        <v>0.159</v>
+        <v>0.9373</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4499</v>
+        <v>-0.3505</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6593</v>
+        <v>-0.2851</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6785</v>
+        <v>0.0424</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9808</v>
+        <v>-0.3275</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8147</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>1.492</v>
+        <v>1.2879</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9599</v>
+        <v>1.0124</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4679</v>
+        <v>0.2755</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3856</v>
+        <v>-1.2472</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3856</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. COOK</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2922</v>
+        <v>-0.3699</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1353</v>
+        <v>0.7504</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4275</v>
+        <v>-1.1203</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3112</v>
+        <v>-1.4944</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9856</v>
+        <v>-0.8497</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6744</v>
+        <v>-0.6446</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6143</v>
+        <v>0.0525</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9555</v>
+        <v>-0.0592</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3413</v>
+        <v>0.1117</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.303</v>
+        <v>-1.5469</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0301</v>
+        <v>-0.7906</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3331</v>
+        <v>-0.7563</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3305</v>
+        <v>0.8757</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2431</v>
+        <v>0.2505</v>
       </c>
       <c r="U19" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.6251</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2534</v>
+        <v>0.9317</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5463</v>
+        <v>2.7237</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4662</v>
+        <v>-0.5966</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7847</v>
+        <v>-0.6931</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2509</v>
+        <v>0.0965</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4956</v>
+        <v>-0.051</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8426</v>
+        <v>-0.5171</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.653</v>
+        <v>0.4661</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0733</v>
+        <v>1.5813</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0386</v>
+        <v>0.1444</v>
       </c>
       <c r="L20" t="n">
-        <v>0.112</v>
+        <v>1.4369</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5689</v>
+        <v>-1.6323</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.6615</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7649</v>
+        <v>-0.9708</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6805</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7779</v>
+        <v>0.8885</v>
       </c>
       <c r="T20" t="n">
-        <v>0.248</v>
+        <v>1.1401</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5299</v>
+        <v>-0.2516</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.387</v>
       </c>
       <c r="W20" t="n">
-        <v>2.7317</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7997</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6704</v>
+        <v>-1.1277</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0732</v>
+        <v>0.3976</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7436</v>
+        <v>-1.5254</v>
       </c>
       <c r="G21" t="n">
-        <v>1.072</v>
+        <v>1.0766</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0102</v>
+        <v>-0.0033</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0822</v>
+        <v>1.0799</v>
       </c>
       <c r="J21" t="n">
-        <v>3.1762</v>
+        <v>3.1551</v>
       </c>
       <c r="K21" t="n">
-        <v>1.8009</v>
+        <v>1.7926</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3753</v>
+        <v>1.3624</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1043</v>
+        <v>-2.0784</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8112</v>
+        <v>-1.7959</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8351</v>
+        <v>-0.2938</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6079</v>
+        <v>-0.2535</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2271</v>
+        <v>-0.0403</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8916</v>
+        <v>-2.45</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.161</v>
+        <v>0.0338</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7306</v>
+        <v>-2.4838</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5685</v>
+        <v>1.5695</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6839</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2524</v>
+        <v>2.2585</v>
       </c>
       <c r="J22" t="n">
-        <v>3.846</v>
+        <v>3.8203</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4577</v>
+        <v>1.4372</v>
       </c>
       <c r="L22" t="n">
-        <v>2.3883</v>
+        <v>2.3832</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.2774</v>
+        <v>-2.2508</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.1416</v>
+        <v>-2.1262</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7381</v>
+        <v>-1.2879</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5383</v>
+        <v>-0.3022</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1998</v>
+        <v>-0.9857</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. SAKHO</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.98</v>
+        <v>-3.3483</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7839</v>
+        <v>0.0235</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.196</v>
+        <v>-3.3718</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.5241</v>
+        <v>-1.754</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.7374</v>
+        <v>-2.2175</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2133</v>
+        <v>0.4635</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0883</v>
+        <v>1.6428</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.163</v>
+        <v>-0.0624</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0746</v>
+        <v>1.7052</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4357</v>
+        <v>-3.3968</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5744</v>
+        <v>-2.1551</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1387</v>
+        <v>-1.2417</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6805</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3173</v>
+        <v>-0.4365</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6654</v>
+        <v>-0.2535</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3481</v>
+        <v>-0.183</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-0.7025</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>J. SAKHO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2741</v>
+        <v>-3.4106</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3039</v>
+        <v>-1.2655</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9702</v>
+        <v>-2.1452</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.7637</v>
+        <v>-1.5141</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.2222</v>
+        <v>-1.7349</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4585</v>
+        <v>0.2208</v>
       </c>
       <c r="J24" t="n">
-        <v>1.665</v>
+        <v>-0.0946</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0488</v>
+        <v>-0.1691</v>
       </c>
       <c r="L24" t="n">
-        <v>1.7139</v>
+        <v>0.0745</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.4287</v>
+        <v>-1.4194</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.1734</v>
+        <v>-1.5658</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2554</v>
+        <v>0.1463</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4537</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3496</v>
+        <v>-0.1242</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6079</v>
+        <v>0.195</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2583</v>
+        <v>-0.3191</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.7071</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.7071</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.6948</v>
+        <v>-4.2143</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.7957</v>
+        <v>-2.588</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8991</v>
+        <v>-1.6263</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.7723</v>
+        <v>-1.7694</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.3939</v>
+        <v>-1.3957</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3785</v>
+        <v>-0.3737</v>
       </c>
       <c r="J25" t="n">
-        <v>0.327</v>
+        <v>0.3078</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1181</v>
+        <v>-0.1314</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.0993</v>
+        <v>-2.0772</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-0.4645</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2419</v>
+        <v>-0.0049</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7071</v>
+        <v>-0.4596</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,64 +2437,64 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.8815</v>
+        <v>-5.1114</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.8005</v>
+        <v>-5.3795</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.081</v>
+        <v>0.2681</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.11</v>
+        <v>-3.1148</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.5871</v>
+        <v>-3.5899</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4771</v>
+        <v>0.4751</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.4458</v>
+        <v>-1.4813</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.3733</v>
+        <v>-2.3969</v>
       </c>
       <c r="L26" t="n">
-        <v>0.9275</v>
+        <v>0.9156</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.6643</v>
+        <v>-1.6335</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.2139</v>
+        <v>-1.1931</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q26" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R26" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2102</v>
+        <v>0.5772</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0212</v>
+        <v>0.4967</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2314</v>
+        <v>0.0805</v>
       </c>
       <c r="V26" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-15.9566</v>
+        <v>-15.1664</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.408</v>
+        <v>-2.727</v>
       </c>
       <c r="F27" t="n">
-        <v>-13.5485</v>
+        <v>-12.4396</v>
       </c>
       <c r="G27" t="n">
-        <v>-5.3293</v>
+        <v>-5.309200000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>-8.9679</v>
+        <v>-8.9748</v>
       </c>
       <c r="I27" t="n">
-        <v>3.6385</v>
+        <v>3.6658</v>
       </c>
       <c r="J27" t="n">
-        <v>13.4886</v>
+        <v>13.2445</v>
       </c>
       <c r="K27" t="n">
-        <v>3.480199999999999</v>
+        <v>3.312099999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>10.0084</v>
+        <v>9.932399999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>-18.8178</v>
+        <v>-18.5536</v>
       </c>
       <c r="N27" t="n">
-        <v>-12.4482</v>
+        <v>-12.2871</v>
       </c>
       <c r="O27" t="n">
-        <v>-6.3698</v>
+        <v>-6.2667</v>
       </c>
       <c r="P27" t="n">
-        <v>-10.2075</v>
+        <v>-10.2435</v>
       </c>
       <c r="Q27" t="n">
-        <v>-23.8175</v>
+        <v>-23.9012</v>
       </c>
       <c r="R27" t="n">
-        <v>13.6099</v>
+        <v>13.6579</v>
       </c>
       <c r="S27" t="n">
-        <v>2.087</v>
+        <v>2.8808</v>
       </c>
       <c r="T27" t="n">
-        <v>3.6145</v>
+        <v>3.6434</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.5273</v>
+        <v>-0.7627</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.5068</v>
+        <v>-2.4944</v>
       </c>
       <c r="W27" t="n">
-        <v>4.3065</v>
+        <v>4.2865</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.8133</v>
+        <v>-6.781</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104682_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104682_W25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-4.2865</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>0</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104682_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-6.781</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
